--- a/Dashboard_Leak/ข้อมูลดิบ/หน่วยไฟ/EU_2569.xlsx
+++ b/Dashboard_Leak/ข้อมูลดิบ/หน่วยไฟ/EU_2569.xlsx
@@ -883,11 +883,11 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="725248726"/>
-        <c:axId val="538382129"/>
+        <c:axId val="1493871916"/>
+        <c:axId val="935188432"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="725248726"/>
+        <c:axId val="1493871916"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -939,10 +939,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="538382129"/>
+        <c:crossAx val="935188432"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="538382129"/>
+        <c:axId val="935188432"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1006,7 +1006,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="725248726"/>
+        <c:crossAx val="1493871916"/>
       </c:valAx>
     </c:plotArea>
     <c:plotVisOnly val="1"/>
@@ -1196,11 +1196,11 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="1820492137"/>
-        <c:axId val="1940280106"/>
+        <c:axId val="1165479712"/>
+        <c:axId val="2015991518"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="1820492137"/>
+        <c:axId val="1165479712"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1252,10 +1252,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1940280106"/>
+        <c:crossAx val="2015991518"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1940280106"/>
+        <c:axId val="2015991518"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1330,7 +1330,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1820492137"/>
+        <c:crossAx val="1165479712"/>
       </c:valAx>
     </c:plotArea>
     <c:plotVisOnly val="1"/>
@@ -1814,11 +1814,11 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="521671297"/>
-        <c:axId val="139963726"/>
+        <c:axId val="1944898062"/>
+        <c:axId val="133583594"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="521671297"/>
+        <c:axId val="1944898062"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1870,10 +1870,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="139963726"/>
+        <c:crossAx val="133583594"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="139963726"/>
+        <c:axId val="133583594"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1948,7 +1948,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="521671297"/>
+        <c:crossAx val="1944898062"/>
       </c:valAx>
     </c:plotArea>
     <c:plotVisOnly val="1"/>
@@ -2059,11 +2059,11 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="1308565832"/>
-        <c:axId val="757168226"/>
+        <c:axId val="317827488"/>
+        <c:axId val="1763929419"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="1308565832"/>
+        <c:axId val="317827488"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2115,10 +2115,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="757168226"/>
+        <c:crossAx val="1763929419"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="757168226"/>
+        <c:axId val="1763929419"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2193,7 +2193,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1308565832"/>
+        <c:crossAx val="317827488"/>
       </c:valAx>
     </c:plotArea>
     <c:plotVisOnly val="1"/>
